--- a/artfynd/A 28796-2024 artfynd.xlsx
+++ b/artfynd/A 28796-2024 artfynd.xlsx
@@ -1391,10 +1391,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119506733</v>
+        <v>119506843</v>
       </c>
       <c r="B8" t="n">
-        <v>90562</v>
+        <v>79607</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1407,21 +1407,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>541453</v>
+        <v>541611</v>
       </c>
       <c r="R8" t="n">
-        <v>7246859</v>
+        <v>7246959</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1469,6 +1469,11 @@
           <t>2024-08-04</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På 2 sälgar</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1480,22 +1485,17 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>Granhögstubbe</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1513,10 +1513,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119506879</v>
+        <v>119506733</v>
       </c>
       <c r="B9" t="n">
-        <v>90576</v>
+        <v>90562</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1529,21 +1529,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1553,10 +1553,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>541392</v>
+        <v>541453</v>
       </c>
       <c r="R9" t="n">
-        <v>7246823</v>
+        <v>7246859</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1610,9 +1610,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>Granhögstubbe</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granhögstubbe</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1630,10 +1635,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119506843</v>
+        <v>119506879</v>
       </c>
       <c r="B10" t="n">
-        <v>79607</v>
+        <v>90576</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1646,21 +1651,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1670,10 +1675,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>541611</v>
+        <v>541392</v>
       </c>
       <c r="R10" t="n">
-        <v>7246959</v>
+        <v>7246823</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1708,11 +1713,6 @@
           <t>2024-08-04</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På 2 sälgar</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1724,17 +1724,17 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -2601,10 +2601,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119506909</v>
+        <v>119506793</v>
       </c>
       <c r="B18" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2617,34 +2617,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>541625</v>
+        <v>541460</v>
       </c>
       <c r="R18" t="n">
-        <v>7247035</v>
+        <v>7246892</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2679,6 +2684,11 @@
           <t>2024-08-04</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Barksprätt, färska</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2698,14 +2708,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL18" t="inlineStr">
-        <is>
-          <t>Granhögstubbe</t>
-        </is>
-      </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2723,7 +2728,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119506886</v>
+        <v>119506909</v>
       </c>
       <c r="B19" t="n">
         <v>90580</v>
@@ -2763,10 +2768,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>541671</v>
+        <v>541625</v>
       </c>
       <c r="R19" t="n">
-        <v>7247092</v>
+        <v>7247035</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2822,12 +2827,12 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>levande</t>
+          <t>Granhögstubbe</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Picea abies # levande</t>
+          <t>Picea abies # Granhögstubbe</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2845,10 +2850,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119506793</v>
+        <v>119506886</v>
       </c>
       <c r="B20" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2861,39 +2866,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>541460</v>
+        <v>541671</v>
       </c>
       <c r="R20" t="n">
-        <v>7246892</v>
+        <v>7247092</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2928,11 +2928,6 @@
           <t>2024-08-04</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Barksprätt, färska</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2952,9 +2947,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>levande</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # levande</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3220,10 +3220,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119506778</v>
+        <v>119506913</v>
       </c>
       <c r="B23" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3236,39 +3236,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>541526</v>
+        <v>541410</v>
       </c>
       <c r="R23" t="n">
-        <v>7247213</v>
+        <v>7246814</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3305,7 +3300,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Barksprätt, färska</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3316,21 +3311,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3469,10 +3449,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119506913</v>
+        <v>119506778</v>
       </c>
       <c r="B25" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3485,34 +3465,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>541410</v>
+        <v>541526</v>
       </c>
       <c r="R25" t="n">
-        <v>7246814</v>
+        <v>7247213</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3549,7 +3534,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Barksprätt, färska</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3560,6 +3545,21 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">

--- a/artfynd/A 28796-2024 artfynd.xlsx
+++ b/artfynd/A 28796-2024 artfynd.xlsx
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119506824</v>
+        <v>119506722</v>
       </c>
       <c r="B5" t="n">
-        <v>91005</v>
+        <v>90905</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,34 +1042,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>2062</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>541480</v>
+        <v>541455</v>
       </c>
       <c r="R5" t="n">
-        <v>7247086</v>
+        <v>7246861</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1104,12 +1107,18 @@
           <t>2024-08-04</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Kollekt På ved under ullticka</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1123,14 +1132,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1148,10 +1152,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119506722</v>
+        <v>119506824</v>
       </c>
       <c r="B6" t="n">
-        <v>90905</v>
+        <v>91005</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1164,37 +1168,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2062</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>541455</v>
+        <v>541480</v>
       </c>
       <c r="R6" t="n">
-        <v>7246861</v>
+        <v>7247086</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1229,18 +1230,12 @@
           <t>2024-08-04</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Kollekt På ved under ullticka</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1254,9 +1249,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -3697,10 +3697,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119506846</v>
+        <v>119506804</v>
       </c>
       <c r="B27" t="n">
-        <v>79607</v>
+        <v>57463</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3713,34 +3713,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>541493</v>
+        <v>541479</v>
       </c>
       <c r="R27" t="n">
-        <v>7247094</v>
+        <v>7247082</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3783,21 +3788,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3814,10 +3804,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119506804</v>
+        <v>119506846</v>
       </c>
       <c r="B28" t="n">
-        <v>57463</v>
+        <v>79607</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3830,39 +3820,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>541479</v>
+        <v>541493</v>
       </c>
       <c r="R28" t="n">
-        <v>7247082</v>
+        <v>7247094</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3905,6 +3890,21 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -4797,10 +4797,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119506794</v>
+        <v>119506735</v>
       </c>
       <c r="B36" t="n">
-        <v>57310</v>
+        <v>91254</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4809,43 +4809,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>541533</v>
+        <v>541604</v>
       </c>
       <c r="R36" t="n">
-        <v>7247171</v>
+        <v>7246915</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4882,7 +4877,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Barksprätt, färska</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4904,9 +4899,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL36" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4924,10 +4924,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119506735</v>
+        <v>119506849</v>
       </c>
       <c r="B37" t="n">
-        <v>91254</v>
+        <v>79607</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4936,25 +4936,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3298</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4964,10 +4964,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>541604</v>
+        <v>541555</v>
       </c>
       <c r="R37" t="n">
-        <v>7246915</v>
+        <v>7247205</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5002,11 +5002,6 @@
           <t>2024-08-04</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5018,22 +5013,17 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL37" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5051,10 +5041,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119506849</v>
+        <v>119506794</v>
       </c>
       <c r="B38" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5067,34 +5057,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>541555</v>
+        <v>541533</v>
       </c>
       <c r="R38" t="n">
-        <v>7247205</v>
+        <v>7247171</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5129,6 +5124,11 @@
           <t>2024-08-04</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Barksprätt, färska</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5140,17 +5140,17 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -6025,10 +6025,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119506883</v>
+        <v>119506855</v>
       </c>
       <c r="B46" t="n">
-        <v>90580</v>
+        <v>79607</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6041,21 +6041,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6065,10 +6065,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>541720</v>
+        <v>541536</v>
       </c>
       <c r="R46" t="n">
-        <v>7247332</v>
+        <v>7246870</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6114,22 +6114,22 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AL46" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Död rönn</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Picea abies # Stubbe</t>
+          <t>Sorbus aucuparia # Död rönn</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6147,10 +6147,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119506855</v>
+        <v>119506883</v>
       </c>
       <c r="B47" t="n">
-        <v>79607</v>
+        <v>90580</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6163,21 +6163,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6187,10 +6187,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>541536</v>
+        <v>541720</v>
       </c>
       <c r="R47" t="n">
-        <v>7246870</v>
+        <v>7247332</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6236,22 +6236,22 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL47" t="inlineStr">
         <is>
-          <t>Död rönn</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia # Död rönn</t>
+          <t>Picea abies # Stubbe</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>

--- a/artfynd/A 28796-2024 artfynd.xlsx
+++ b/artfynd/A 28796-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119506932</v>
+        <v>119506849</v>
       </c>
       <c r="B2" t="n">
-        <v>90957</v>
+        <v>79607</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4217</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>541480</v>
+        <v>541555</v>
       </c>
       <c r="R2" t="n">
-        <v>7247090</v>
+        <v>7247205</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -764,17 +764,17 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119506848</v>
+        <v>119506822</v>
       </c>
       <c r="B3" t="n">
-        <v>79607</v>
+        <v>91005</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,25 +804,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>541498</v>
+        <v>541602</v>
       </c>
       <c r="R3" t="n">
-        <v>7247159</v>
+        <v>7246889</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,17 +881,22 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>Granlåga grov</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies # Granlåga grov</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -909,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119506858</v>
+        <v>119506754</v>
       </c>
       <c r="B4" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,34 +930,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>541499</v>
+        <v>541563</v>
       </c>
       <c r="R4" t="n">
-        <v>7246880</v>
+        <v>7247188</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,6 +997,11 @@
           <t>2024-08-04</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -998,17 +1013,17 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1026,10 +1041,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119506722</v>
+        <v>119506878</v>
       </c>
       <c r="B5" t="n">
-        <v>90905</v>
+        <v>90576</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,41 +1053,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2062</v>
+        <v>1204</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>541455</v>
+        <v>541706</v>
       </c>
       <c r="R5" t="n">
-        <v>7246861</v>
+        <v>7247345</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1107,18 +1119,12 @@
           <t>2024-08-04</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Kollekt På ved under ullticka</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1132,9 +1138,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1152,10 +1163,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119506824</v>
+        <v>119506910</v>
       </c>
       <c r="B6" t="n">
-        <v>91005</v>
+        <v>90580</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1164,25 +1175,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1192,10 +1203,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>541480</v>
+        <v>541493</v>
       </c>
       <c r="R6" t="n">
-        <v>7247086</v>
+        <v>7246877</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1251,12 +1262,12 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Granhögstubbe</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Picea abies # Granhögstubbe</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1274,10 +1285,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119506852</v>
+        <v>119506722</v>
       </c>
       <c r="B7" t="n">
-        <v>79607</v>
+        <v>90905</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1286,38 +1297,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>2062</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>541629</v>
+        <v>541455</v>
       </c>
       <c r="R7" t="n">
-        <v>7246933</v>
+        <v>7246861</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1352,28 +1366,34 @@
           <t>2024-08-04</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Kollekt På ved under ullticka</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1391,10 +1411,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119506843</v>
+        <v>119506737</v>
       </c>
       <c r="B8" t="n">
-        <v>79607</v>
+        <v>91254</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1403,25 +1423,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>3298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1431,10 +1451,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>541611</v>
+        <v>541455</v>
       </c>
       <c r="R8" t="n">
-        <v>7246959</v>
+        <v>7246861</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1471,7 +1491,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På 2 sälgar</t>
+          <t>Fjolårets fruktkroppar, vid basen</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1485,17 +1505,22 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1513,10 +1538,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119506733</v>
+        <v>119506852</v>
       </c>
       <c r="B9" t="n">
-        <v>90562</v>
+        <v>79607</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1529,21 +1554,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1553,10 +1578,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>541453</v>
+        <v>541629</v>
       </c>
       <c r="R9" t="n">
-        <v>7246859</v>
+        <v>7246933</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1602,22 +1627,17 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>Granhögstubbe</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1635,10 +1655,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119506879</v>
+        <v>119506784</v>
       </c>
       <c r="B10" t="n">
-        <v>90576</v>
+        <v>57310</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1651,34 +1671,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>541392</v>
+        <v>541374</v>
       </c>
       <c r="R10" t="n">
-        <v>7246823</v>
+        <v>7246832</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1711,6 +1736,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1752,10 +1782,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119506826</v>
+        <v>119506779</v>
       </c>
       <c r="B11" t="n">
-        <v>91005</v>
+        <v>57310</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1764,38 +1794,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>541453</v>
+        <v>541700</v>
       </c>
       <c r="R11" t="n">
-        <v>7246866</v>
+        <v>7247194</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1830,6 +1865,11 @@
           <t>2024-08-04</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Barksprätt, färska</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1849,14 +1889,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1874,10 +1909,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119506878</v>
+        <v>119506836</v>
       </c>
       <c r="B12" t="n">
-        <v>90576</v>
+        <v>90846</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1890,34 +1925,38 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>541706</v>
+        <v>541458</v>
       </c>
       <c r="R12" t="n">
-        <v>7247345</v>
+        <v>7246865</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1996,10 +2035,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119506856</v>
+        <v>119506913</v>
       </c>
       <c r="B13" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2012,21 +2051,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2036,10 +2075,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>541590</v>
+        <v>541410</v>
       </c>
       <c r="R13" t="n">
-        <v>7246904</v>
+        <v>7246814</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2076,7 +2115,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På 2 rönnar</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2087,21 +2126,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2118,10 +2142,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119506884</v>
+        <v>119506820</v>
       </c>
       <c r="B14" t="n">
-        <v>90580</v>
+        <v>91005</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2130,25 +2154,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2158,10 +2182,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>541591</v>
+        <v>541676</v>
       </c>
       <c r="R14" t="n">
-        <v>7246903</v>
+        <v>7247147</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2217,12 +2241,12 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>Lutande död gran</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Picea abies # Lutande död gran</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2240,10 +2264,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119506910</v>
+        <v>119506858</v>
       </c>
       <c r="B15" t="n">
-        <v>90580</v>
+        <v>79607</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2256,21 +2280,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2280,10 +2304,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>541493</v>
+        <v>541499</v>
       </c>
       <c r="R15" t="n">
-        <v>7246877</v>
+        <v>7246880</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2329,22 +2353,17 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL15" t="inlineStr">
-        <is>
-          <t>Granhögstubbe</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2362,10 +2381,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119506881</v>
+        <v>119506855</v>
       </c>
       <c r="B16" t="n">
-        <v>90576</v>
+        <v>79607</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2378,21 +2397,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2402,10 +2421,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>541753</v>
+        <v>541536</v>
       </c>
       <c r="R16" t="n">
-        <v>7247186</v>
+        <v>7246870</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2451,22 +2470,22 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>Granlåga, avbarkad</t>
+          <t>Död rönn</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga, avbarkad</t>
+          <t>Sorbus aucuparia # Död rönn</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2484,10 +2503,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119506857</v>
+        <v>119506901</v>
       </c>
       <c r="B17" t="n">
-        <v>79607</v>
+        <v>90580</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2500,21 +2519,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2524,10 +2543,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>541453</v>
+        <v>541688</v>
       </c>
       <c r="R17" t="n">
-        <v>7246885</v>
+        <v>7247332</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2573,17 +2592,22 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2601,10 +2625,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119506793</v>
+        <v>119506873</v>
       </c>
       <c r="B18" t="n">
-        <v>57310</v>
+        <v>90558</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2617,39 +2641,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>541460</v>
+        <v>541547</v>
       </c>
       <c r="R18" t="n">
-        <v>7246892</v>
+        <v>7247185</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2684,11 +2703,6 @@
           <t>2024-08-04</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Barksprätt, färska</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2708,9 +2722,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>Granhögstubbe</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granhögstubbe</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2728,10 +2747,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119506909</v>
+        <v>119506804</v>
       </c>
       <c r="B19" t="n">
-        <v>90580</v>
+        <v>57463</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2744,34 +2763,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>541625</v>
+        <v>541479</v>
       </c>
       <c r="R19" t="n">
-        <v>7247035</v>
+        <v>7247082</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2814,26 +2838,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL19" t="inlineStr">
-        <is>
-          <t>Granhögstubbe</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Picea abies # Granhögstubbe</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2850,10 +2854,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119506886</v>
+        <v>119506880</v>
       </c>
       <c r="B20" t="n">
-        <v>90580</v>
+        <v>90576</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2866,21 +2870,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2890,10 +2894,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>541671</v>
+        <v>541599</v>
       </c>
       <c r="R20" t="n">
-        <v>7247092</v>
+        <v>7246887</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2949,12 +2953,12 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>levande</t>
+          <t>Granlåga, grov</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Picea abies # levande</t>
+          <t>Picea abies # Granlåga, grov</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2972,10 +2976,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119506836</v>
+        <v>119506882</v>
       </c>
       <c r="B21" t="n">
-        <v>90846</v>
+        <v>90576</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2988,38 +2992,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>541458</v>
+        <v>541553</v>
       </c>
       <c r="R21" t="n">
-        <v>7246865</v>
+        <v>7247198</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3098,10 +3098,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119506822</v>
+        <v>119506850</v>
       </c>
       <c r="B22" t="n">
-        <v>91005</v>
+        <v>79607</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3110,25 +3110,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3138,10 +3138,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>541602</v>
+        <v>541544</v>
       </c>
       <c r="R22" t="n">
-        <v>7246889</v>
+        <v>7247215</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3187,22 +3187,17 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL22" t="inlineStr">
-        <is>
-          <t>Granlåga grov</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga grov</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3220,10 +3215,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119506913</v>
+        <v>119506851</v>
       </c>
       <c r="B23" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3236,21 +3231,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3260,10 +3255,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>541410</v>
+        <v>541616</v>
       </c>
       <c r="R23" t="n">
-        <v>7246814</v>
+        <v>7246971</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3298,11 +3293,6 @@
           <t>2024-08-04</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3311,6 +3301,21 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3327,10 +3332,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119506901</v>
+        <v>119506846</v>
       </c>
       <c r="B24" t="n">
-        <v>90580</v>
+        <v>79607</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3343,21 +3348,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3367,10 +3372,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>541688</v>
+        <v>541493</v>
       </c>
       <c r="R24" t="n">
-        <v>7247332</v>
+        <v>7247094</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3416,22 +3421,17 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL24" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3449,10 +3449,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119506778</v>
+        <v>119506883</v>
       </c>
       <c r="B25" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3465,39 +3465,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>541526</v>
+        <v>541720</v>
       </c>
       <c r="R25" t="n">
-        <v>7247213</v>
+        <v>7247332</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3532,11 +3527,6 @@
           <t>2024-08-04</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Barksprätt, färska</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3556,9 +3546,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Stubbe</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3576,10 +3571,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119506861</v>
+        <v>119506884</v>
       </c>
       <c r="B26" t="n">
-        <v>90954</v>
+        <v>90580</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3592,32 +3587,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6040186</v>
+        <v>5432</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>541546</v>
+        <v>541591</v>
       </c>
       <c r="R26" t="n">
-        <v>7247187</v>
+        <v>7246903</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3658,7 +3655,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3674,12 +3670,12 @@
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>Granhögstubbe</t>
+          <t>Lutande död gran</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe</t>
+          <t>Picea abies # Lutande död gran</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3697,10 +3693,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119506804</v>
+        <v>119506881</v>
       </c>
       <c r="B27" t="n">
-        <v>57463</v>
+        <v>90576</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3713,39 +3709,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>1204</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>541479</v>
+        <v>541753</v>
       </c>
       <c r="R27" t="n">
-        <v>7247082</v>
+        <v>7247186</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3788,6 +3779,26 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL27" t="inlineStr">
+        <is>
+          <t>Granlåga, avbarkad</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga, avbarkad</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3804,10 +3815,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119506846</v>
+        <v>119506821</v>
       </c>
       <c r="B28" t="n">
-        <v>79607</v>
+        <v>91005</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3816,25 +3827,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3844,10 +3855,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>541493</v>
+        <v>541524</v>
       </c>
       <c r="R28" t="n">
-        <v>7247094</v>
+        <v>7247178</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3893,17 +3904,22 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL28" t="inlineStr">
+        <is>
+          <t>Granlåga grov</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies # Granlåga grov</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3921,10 +3937,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119506902</v>
+        <v>119506825</v>
       </c>
       <c r="B29" t="n">
-        <v>90580</v>
+        <v>91005</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3933,25 +3949,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3961,10 +3977,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>541589</v>
+        <v>541556</v>
       </c>
       <c r="R29" t="n">
-        <v>7246895</v>
+        <v>7247196</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4043,10 +4059,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119506860</v>
+        <v>119506843</v>
       </c>
       <c r="B30" t="n">
-        <v>90954</v>
+        <v>79607</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4059,32 +4075,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6040186</v>
+        <v>6458</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>541527</v>
+        <v>541611</v>
       </c>
       <c r="R30" t="n">
-        <v>7247215</v>
+        <v>7246959</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4119,34 +4137,33 @@
           <t>2024-08-04</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På 2 sälgar</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL30" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4426,10 +4443,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119506737</v>
+        <v>119506794</v>
       </c>
       <c r="B33" t="n">
-        <v>91254</v>
+        <v>57310</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4438,38 +4455,43 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>541455</v>
+        <v>541533</v>
       </c>
       <c r="R33" t="n">
-        <v>7246861</v>
+        <v>7247171</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4506,7 +4528,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Fjolårets fruktkroppar, vid basen</t>
+          <t>Barksprätt, färska</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4528,14 +4550,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL33" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4553,10 +4570,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119506850</v>
+        <v>119506879</v>
       </c>
       <c r="B34" t="n">
-        <v>79607</v>
+        <v>90576</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4569,21 +4586,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4593,10 +4610,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>541544</v>
+        <v>541392</v>
       </c>
       <c r="R34" t="n">
-        <v>7247215</v>
+        <v>7246823</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4642,17 +4659,17 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4670,10 +4687,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119506784</v>
+        <v>119506886</v>
       </c>
       <c r="B35" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4686,39 +4703,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>541374</v>
+        <v>541671</v>
       </c>
       <c r="R35" t="n">
-        <v>7246832</v>
+        <v>7247092</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4753,11 +4765,6 @@
           <t>2024-08-04</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4777,9 +4784,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL35" t="inlineStr">
+        <is>
+          <t>levande</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # levande</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4797,10 +4809,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119506735</v>
+        <v>119506778</v>
       </c>
       <c r="B36" t="n">
-        <v>91254</v>
+        <v>57310</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4809,38 +4821,43 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>541604</v>
+        <v>541526</v>
       </c>
       <c r="R36" t="n">
-        <v>7246915</v>
+        <v>7247213</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4877,7 +4894,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Barksprätt, färska</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4899,14 +4916,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL36" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4924,10 +4936,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119506849</v>
+        <v>119506783</v>
       </c>
       <c r="B37" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4940,34 +4952,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>541555</v>
+        <v>541672</v>
       </c>
       <c r="R37" t="n">
-        <v>7247205</v>
+        <v>7247167</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5002,6 +5019,11 @@
           <t>2024-08-04</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5013,17 +5035,17 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5041,10 +5063,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119506794</v>
+        <v>119506733</v>
       </c>
       <c r="B38" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5057,39 +5079,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>541533</v>
+        <v>541453</v>
       </c>
       <c r="R38" t="n">
-        <v>7247171</v>
+        <v>7246859</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5124,11 +5141,6 @@
           <t>2024-08-04</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Barksprätt, färska</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5148,9 +5160,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL38" t="inlineStr">
+        <is>
+          <t>Granhögstubbe</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granhögstubbe</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5168,10 +5185,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119506820</v>
+        <v>119506739</v>
       </c>
       <c r="B39" t="n">
-        <v>91005</v>
+        <v>91254</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5180,25 +5197,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1209</v>
+        <v>3298</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5208,10 +5225,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>541676</v>
+        <v>541700</v>
       </c>
       <c r="R39" t="n">
-        <v>7247147</v>
+        <v>7247194</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5246,6 +5263,11 @@
           <t>2024-08-04</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Vid basen</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -5265,14 +5287,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL39" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5290,10 +5307,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119506825</v>
+        <v>119506848</v>
       </c>
       <c r="B40" t="n">
-        <v>91005</v>
+        <v>79607</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5302,25 +5319,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5330,10 +5347,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>541556</v>
+        <v>541498</v>
       </c>
       <c r="R40" t="n">
-        <v>7247196</v>
+        <v>7247159</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5379,22 +5396,17 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL40" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5412,7 +5424,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119506844</v>
+        <v>119506856</v>
       </c>
       <c r="B41" t="n">
         <v>79607</v>
@@ -5452,10 +5464,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>541477</v>
+        <v>541590</v>
       </c>
       <c r="R41" t="n">
-        <v>7246915</v>
+        <v>7246904</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5490,6 +5502,11 @@
           <t>2024-08-04</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På 2 rönnar</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5501,17 +5518,17 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5651,10 +5668,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119506862</v>
+        <v>119506932</v>
       </c>
       <c r="B43" t="n">
-        <v>90954</v>
+        <v>90957</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5663,40 +5680,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6040186</v>
+        <v>4217</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Blodticka</t>
+        </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>541476</v>
+        <v>541480</v>
       </c>
       <c r="R43" t="n">
-        <v>7247094</v>
+        <v>7247090</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5731,18 +5746,12 @@
           <t>2024-08-04</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Minst 22 fruktkroppar</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5756,14 +5765,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL43" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5781,10 +5785,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119506845</v>
+        <v>119506735</v>
       </c>
       <c r="B44" t="n">
-        <v>79607</v>
+        <v>91254</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5793,25 +5797,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>3298</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5821,10 +5825,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>541496</v>
+        <v>541604</v>
       </c>
       <c r="R44" t="n">
-        <v>7247059</v>
+        <v>7246915</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5859,6 +5863,11 @@
           <t>2024-08-04</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5870,17 +5879,22 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL44" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5898,10 +5912,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119506771</v>
+        <v>119506845</v>
       </c>
       <c r="B45" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5914,39 +5928,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>541407</v>
+        <v>541496</v>
       </c>
       <c r="R45" t="n">
-        <v>7246819</v>
+        <v>7247059</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5981,11 +5990,6 @@
           <t>2024-08-04</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack, färska</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5997,17 +6001,17 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6025,10 +6029,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119506855</v>
+        <v>119506793</v>
       </c>
       <c r="B46" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6041,34 +6045,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>541536</v>
+        <v>541460</v>
       </c>
       <c r="R46" t="n">
-        <v>7246870</v>
+        <v>7246892</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6103,6 +6112,11 @@
           <t>2024-08-04</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Barksprätt, färska</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -6114,22 +6128,17 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AL46" t="inlineStr">
-        <is>
-          <t>Död rönn</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia # Död rönn</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6147,10 +6156,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119506883</v>
+        <v>119506862</v>
       </c>
       <c r="B47" t="n">
-        <v>90580</v>
+        <v>90954</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6163,34 +6172,36 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>541720</v>
+        <v>541476</v>
       </c>
       <c r="R47" t="n">
-        <v>7247332</v>
+        <v>7247094</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6225,12 +6236,18 @@
           <t>2024-08-04</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Minst 22 fruktkroppar</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6246,12 +6263,12 @@
       </c>
       <c r="AL47" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Picea abies # Stubbe</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6269,10 +6286,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119506880</v>
+        <v>119506860</v>
       </c>
       <c r="B48" t="n">
-        <v>90576</v>
+        <v>90954</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6285,34 +6302,32 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1204</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Gränsticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>541599</v>
+        <v>541527</v>
       </c>
       <c r="R48" t="n">
-        <v>7246887</v>
+        <v>7247215</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6353,6 +6368,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6368,12 +6384,12 @@
       </c>
       <c r="AL48" t="inlineStr">
         <is>
-          <t>Granlåga, grov</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga, grov</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6391,10 +6407,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119506882</v>
+        <v>119506861</v>
       </c>
       <c r="B49" t="n">
-        <v>90576</v>
+        <v>90954</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6407,34 +6423,32 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1204</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Gränsticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>541553</v>
+        <v>541546</v>
       </c>
       <c r="R49" t="n">
-        <v>7247198</v>
+        <v>7247187</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6475,6 +6489,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6490,12 +6505,12 @@
       </c>
       <c r="AL49" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Granhögstubbe</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Picea abies # Granhögstubbe</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6513,10 +6528,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119506783</v>
+        <v>119506826</v>
       </c>
       <c r="B50" t="n">
-        <v>57310</v>
+        <v>91005</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6525,43 +6540,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>541672</v>
+        <v>541453</v>
       </c>
       <c r="R50" t="n">
-        <v>7247167</v>
+        <v>7246866</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6596,11 +6606,6 @@
           <t>2024-08-04</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -6620,9 +6625,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL50" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6640,10 +6650,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119506900</v>
+        <v>119506824</v>
       </c>
       <c r="B51" t="n">
-        <v>90580</v>
+        <v>91005</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6652,25 +6662,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6680,10 +6690,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>541530</v>
+        <v>541480</v>
       </c>
       <c r="R51" t="n">
-        <v>7247230</v>
+        <v>7247086</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6762,10 +6772,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119506833</v>
+        <v>119506844</v>
       </c>
       <c r="B52" t="n">
-        <v>90846</v>
+        <v>79607</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6778,38 +6788,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>541476</v>
+        <v>541477</v>
       </c>
       <c r="R52" t="n">
-        <v>7247092</v>
+        <v>7246915</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6855,22 +6861,17 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL52" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6888,10 +6889,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119506873</v>
+        <v>119506909</v>
       </c>
       <c r="B53" t="n">
-        <v>90558</v>
+        <v>90580</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6904,21 +6905,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6928,10 +6929,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>541547</v>
+        <v>541625</v>
       </c>
       <c r="R53" t="n">
-        <v>7247185</v>
+        <v>7247035</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7010,10 +7011,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119506851</v>
+        <v>119506902</v>
       </c>
       <c r="B54" t="n">
-        <v>79607</v>
+        <v>90580</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7026,21 +7027,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -7050,10 +7051,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>541616</v>
+        <v>541589</v>
       </c>
       <c r="R54" t="n">
-        <v>7246971</v>
+        <v>7246895</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7099,17 +7100,22 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL54" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7127,10 +7133,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119506739</v>
+        <v>119506833</v>
       </c>
       <c r="B55" t="n">
-        <v>91254</v>
+        <v>90846</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7139,38 +7145,42 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3298</v>
+        <v>658</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>541700</v>
+        <v>541476</v>
       </c>
       <c r="R55" t="n">
-        <v>7247194</v>
+        <v>7247092</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7205,11 +7215,6 @@
           <t>2024-08-04</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Vid basen</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -7229,9 +7234,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL55" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7249,10 +7259,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119506754</v>
+        <v>119506801</v>
       </c>
       <c r="B56" t="n">
-        <v>57310</v>
+        <v>56522</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7261,31 +7271,35 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -7294,10 +7308,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>541563</v>
+        <v>541465</v>
       </c>
       <c r="R56" t="n">
-        <v>7247188</v>
+        <v>7247101</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7324,17 +7338,17 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack, äldre</t>
+          <t>Stöttes</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7345,21 +7359,6 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -7376,10 +7375,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119506801</v>
+        <v>119506857</v>
       </c>
       <c r="B57" t="n">
-        <v>56522</v>
+        <v>79607</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7388,47 +7387,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>541465</v>
+        <v>541453</v>
       </c>
       <c r="R57" t="n">
-        <v>7247101</v>
+        <v>7246885</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7455,17 +7445,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-08-04</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Stöttes</t>
+          <t>2024-08-04</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7476,6 +7461,21 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -7492,10 +7492,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119506821</v>
+        <v>119506771</v>
       </c>
       <c r="B58" t="n">
-        <v>91005</v>
+        <v>57310</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7504,38 +7504,43 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>541524</v>
+        <v>541407</v>
       </c>
       <c r="R58" t="n">
-        <v>7247178</v>
+        <v>7246819</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7570,6 +7575,11 @@
           <t>2024-08-04</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack, färska</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -7589,14 +7599,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL58" t="inlineStr">
-        <is>
-          <t>Granlåga grov</t>
-        </is>
-      </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga grov</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7614,7 +7619,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119506779</v>
+        <v>119506782</v>
       </c>
       <c r="B59" t="n">
         <v>57310</v>
@@ -7650,7 +7655,7 @@
       <c r="I59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -7659,10 +7664,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>541700</v>
+        <v>541469</v>
       </c>
       <c r="R59" t="n">
-        <v>7247194</v>
+        <v>7246839</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7699,7 +7704,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Barksprätt, färska</t>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7741,10 +7746,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119506782</v>
+        <v>119506900</v>
       </c>
       <c r="B60" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7757,39 +7762,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>541469</v>
+        <v>541530</v>
       </c>
       <c r="R60" t="n">
-        <v>7246839</v>
+        <v>7247230</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7824,11 +7824,6 @@
           <t>2024-08-04</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -7848,9 +7843,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL60" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>

--- a/artfynd/A 28796-2024 artfynd.xlsx
+++ b/artfynd/A 28796-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY60"/>
+  <dimension ref="A1:AY61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7866,6 +7866,132 @@
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>119506877</v>
+      </c>
+      <c r="B61" t="n">
+        <v>91294</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>1179</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Gräddticka</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Perenniporia subacida</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Peck) Donk</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Matsdal, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>541388</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7246830</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Kollekt Artbestämnd via mikroskopering</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28796-2024 artfynd.xlsx
+++ b/artfynd/A 28796-2024 artfynd.xlsx
@@ -7871,7 +7871,7 @@
         <v>119506877</v>
       </c>
       <c r="B61" t="n">
-        <v>91294</v>
+        <v>91295</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>

--- a/artfynd/A 28796-2024 artfynd.xlsx
+++ b/artfynd/A 28796-2024 artfynd.xlsx
@@ -7871,7 +7871,7 @@
         <v>119506877</v>
       </c>
       <c r="B61" t="n">
-        <v>91303</v>
+        <v>91317</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>

--- a/artfynd/A 28796-2024 artfynd.xlsx
+++ b/artfynd/A 28796-2024 artfynd.xlsx
@@ -7871,12 +7871,7 @@
         <v>119506877</v>
       </c>
       <c r="B61" t="n">
-        <v>91317</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91832</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 28796-2024 artfynd.xlsx
+++ b/artfynd/A 28796-2024 artfynd.xlsx
@@ -7871,7 +7871,7 @@
         <v>119506877</v>
       </c>
       <c r="B61" t="n">
-        <v>91832</v>
+        <v>91906</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 28796-2024 artfynd.xlsx
+++ b/artfynd/A 28796-2024 artfynd.xlsx
@@ -7871,7 +7871,7 @@
         <v>119506877</v>
       </c>
       <c r="B61" t="n">
-        <v>91906</v>
+        <v>91912</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 28796-2024 artfynd.xlsx
+++ b/artfynd/A 28796-2024 artfynd.xlsx
@@ -7871,7 +7871,7 @@
         <v>119506877</v>
       </c>
       <c r="B61" t="n">
-        <v>91912</v>
+        <v>91906</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 28796-2024 artfynd.xlsx
+++ b/artfynd/A 28796-2024 artfynd.xlsx
@@ -1123,7 +1123,7 @@
         <v>0</v>
       </c>
       <c r="AE5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG5" t="b">
         <v>0</v>
@@ -1375,7 +1375,7 @@
         <v>0</v>
       </c>
       <c r="AE7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
@@ -4652,7 +4652,7 @@
         <v>0</v>
       </c>
       <c r="AE34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG34" t="b">
         <v>0</v>
@@ -7871,7 +7871,7 @@
         <v>119506877</v>
       </c>
       <c r="B61" t="n">
-        <v>91906</v>
+        <v>91912</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 28796-2024 artfynd.xlsx
+++ b/artfynd/A 28796-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY61"/>
+  <dimension ref="A1:AY58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119506849</v>
+        <v>119506833</v>
       </c>
       <c r="B2" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,38 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>541555</v>
+        <v>541476</v>
       </c>
       <c r="R2" t="n">
-        <v>7247205</v>
+        <v>7247092</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -764,17 +763,22 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -792,50 +796,49 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119506822</v>
+        <v>119506836</v>
       </c>
       <c r="B3" t="n">
-        <v>91005</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>541602</v>
+        <v>541458</v>
       </c>
       <c r="R3" t="n">
-        <v>7246889</v>
+        <v>7246865</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -891,12 +894,12 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>Granlåga grov</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga grov</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -914,15 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119506754</v>
+        <v>119506871</v>
       </c>
       <c r="B4" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -930,39 +928,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>541563</v>
+        <v>541296</v>
       </c>
       <c r="R4" t="n">
-        <v>7247188</v>
+        <v>7246784</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,14 +992,14 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack, äldre</t>
+          <t>Fjolårets fruktkroppar</t>
         </is>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG4" t="b">
         <v>0</v>
@@ -1041,15 +1034,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119506878</v>
+        <v>119506873</v>
       </c>
       <c r="B5" t="n">
-        <v>90576</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1057,21 +1045,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1204</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1081,10 +1069,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>541706</v>
+        <v>541547</v>
       </c>
       <c r="R5" t="n">
-        <v>7247345</v>
+        <v>7247185</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1123,7 +1111,7 @@
         <v>0</v>
       </c>
       <c r="AE5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="b">
         <v>0</v>
@@ -1140,12 +1128,12 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Granhögstubbe</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Picea abies # Granhögstubbe</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1163,50 +1151,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119506910</v>
+        <v>119506877</v>
       </c>
       <c r="B6" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92522</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>1179</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>541493</v>
+        <v>541388</v>
       </c>
       <c r="R6" t="n">
-        <v>7246877</v>
+        <v>7246830</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1241,12 +1227,18 @@
           <t>2024-08-04</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Kollekt Artbestämnd via mikroskopering</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1260,14 +1252,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>Granhögstubbe</t>
-        </is>
-      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1285,53 +1272,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119506722</v>
+        <v>119506733</v>
       </c>
       <c r="B7" t="n">
-        <v>90905</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>541455</v>
+        <v>541453</v>
       </c>
       <c r="R7" t="n">
-        <v>7246861</v>
+        <v>7246859</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1366,18 +1345,12 @@
           <t>2024-08-04</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Kollekt På ved under ullticka</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF7" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1391,9 +1364,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>Granhögstubbe</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granhögstubbe</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1411,37 +1389,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119506737</v>
+        <v>119506878</v>
       </c>
       <c r="B8" t="n">
-        <v>91254</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3298</v>
+        <v>1204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1451,10 +1424,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>541455</v>
+        <v>541706</v>
       </c>
       <c r="R8" t="n">
-        <v>7246861</v>
+        <v>7247345</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1489,16 +1462,11 @@
           <t>2024-08-04</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Fjolårets fruktkroppar, vid basen</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG8" t="b">
         <v>0</v>
@@ -1538,37 +1506,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119506852</v>
+        <v>119506879</v>
       </c>
       <c r="B9" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1578,10 +1541,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>541629</v>
+        <v>541392</v>
       </c>
       <c r="R9" t="n">
-        <v>7246933</v>
+        <v>7246823</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1620,24 +1583,24 @@
         <v>0</v>
       </c>
       <c r="AE9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1655,55 +1618,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119506784</v>
+        <v>119506880</v>
       </c>
       <c r="B10" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>541374</v>
+        <v>541599</v>
       </c>
       <c r="R10" t="n">
-        <v>7246832</v>
+        <v>7246887</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1738,11 +1691,6 @@
           <t>2024-08-04</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1762,9 +1710,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>Granlåga, grov</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granlåga, grov</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1782,55 +1735,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119506779</v>
+        <v>119506881</v>
       </c>
       <c r="B11" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>541700</v>
+        <v>541753</v>
       </c>
       <c r="R11" t="n">
-        <v>7247194</v>
+        <v>7247186</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1865,11 +1808,6 @@
           <t>2024-08-04</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Barksprätt, färska</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1889,9 +1827,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>Granlåga, avbarkad</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granlåga, avbarkad</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1909,54 +1852,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119506836</v>
+        <v>119506882</v>
       </c>
       <c r="B12" t="n">
-        <v>90846</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>541458</v>
+        <v>541553</v>
       </c>
       <c r="R12" t="n">
-        <v>7246865</v>
+        <v>7247198</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2035,15 +1969,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119506913</v>
+        <v>119506819</v>
       </c>
       <c r="B13" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2051,21 +1980,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2075,10 +2004,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>541410</v>
+        <v>541633</v>
       </c>
       <c r="R13" t="n">
-        <v>7246814</v>
+        <v>7246883</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2113,11 +2042,6 @@
           <t>2024-08-04</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2126,6 +2050,26 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2145,16 +2089,11 @@
         <v>119506820</v>
       </c>
       <c r="B14" t="n">
-        <v>91005</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2167,12 +2106,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2264,15 +2203,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119506858</v>
+        <v>119506821</v>
       </c>
       <c r="B15" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2280,21 +2214,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2304,10 +2238,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>541499</v>
+        <v>541524</v>
       </c>
       <c r="R15" t="n">
-        <v>7246880</v>
+        <v>7247178</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2353,17 +2287,22 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>Granlåga grov</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies # Granlåga grov</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2381,15 +2320,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119506855</v>
+        <v>119506822</v>
       </c>
       <c r="B16" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2397,21 +2331,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2421,10 +2355,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>541536</v>
+        <v>541602</v>
       </c>
       <c r="R16" t="n">
-        <v>7246870</v>
+        <v>7246889</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2470,22 +2404,22 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>Död rönn</t>
+          <t>Granlåga grov</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia # Död rönn</t>
+          <t>Picea abies # Granlåga grov</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2503,15 +2437,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119506901</v>
+        <v>119506824</v>
       </c>
       <c r="B17" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2519,21 +2448,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2543,10 +2472,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>541688</v>
+        <v>541480</v>
       </c>
       <c r="R17" t="n">
-        <v>7247332</v>
+        <v>7247086</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2625,15 +2554,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119506873</v>
+        <v>119506825</v>
       </c>
       <c r="B18" t="n">
-        <v>90558</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2641,21 +2565,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>1209</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2665,10 +2589,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>541547</v>
+        <v>541556</v>
       </c>
       <c r="R18" t="n">
-        <v>7247185</v>
+        <v>7247196</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2724,12 +2648,12 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>Granhögstubbe</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2747,15 +2671,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119506804</v>
+        <v>119506826</v>
       </c>
       <c r="B19" t="n">
-        <v>57463</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2763,39 +2682,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>1209</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>541479</v>
+        <v>541453</v>
       </c>
       <c r="R19" t="n">
-        <v>7247082</v>
+        <v>7246866</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2838,6 +2752,26 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2854,37 +2788,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119506880</v>
+        <v>119506735</v>
       </c>
       <c r="B20" t="n">
-        <v>90576</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1204</v>
+        <v>3298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2894,10 +2823,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>541599</v>
+        <v>541604</v>
       </c>
       <c r="R20" t="n">
-        <v>7246887</v>
+        <v>7246915</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2932,6 +2861,11 @@
           <t>2024-08-04</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2953,12 +2887,12 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>Granlåga, grov</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga, grov</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2976,37 +2910,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119506882</v>
+        <v>119506737</v>
       </c>
       <c r="B21" t="n">
-        <v>90576</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1204</v>
+        <v>3298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3016,10 +2945,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>541553</v>
+        <v>541455</v>
       </c>
       <c r="R21" t="n">
-        <v>7247198</v>
+        <v>7246861</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3052,6 +2981,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Fjolårets fruktkroppar, vid basen</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3098,37 +3032,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119506850</v>
+        <v>119506739</v>
       </c>
       <c r="B22" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>3298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3138,10 +3067,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>541544</v>
+        <v>541700</v>
       </c>
       <c r="R22" t="n">
-        <v>7247215</v>
+        <v>7247194</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3176,6 +3105,11 @@
           <t>2024-08-04</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Vid basen</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3187,17 +3121,17 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3215,37 +3149,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119506851</v>
+        <v>119506932</v>
       </c>
       <c r="B23" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92333</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>4217</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3255,10 +3184,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>541616</v>
+        <v>541480</v>
       </c>
       <c r="R23" t="n">
-        <v>7246971</v>
+        <v>7247090</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3304,17 +3233,17 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3332,37 +3261,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119506846</v>
+        <v>119506913</v>
       </c>
       <c r="B24" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3372,10 +3296,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>541493</v>
+        <v>541410</v>
       </c>
       <c r="R24" t="n">
-        <v>7247094</v>
+        <v>7246814</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3410,6 +3334,11 @@
           <t>2024-08-04</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3418,21 +3347,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3449,15 +3363,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119506883</v>
+        <v>119506842</v>
       </c>
       <c r="B25" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3465,21 +3374,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3489,10 +3398,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>541720</v>
+        <v>541629</v>
       </c>
       <c r="R25" t="n">
-        <v>7247332</v>
+        <v>7246917</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3527,6 +3436,11 @@
           <t>2024-08-04</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3538,22 +3452,17 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL25" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Picea abies # Stubbe</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3571,15 +3480,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119506884</v>
+        <v>119506843</v>
       </c>
       <c r="B26" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3587,21 +3491,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3611,10 +3515,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>541591</v>
+        <v>541611</v>
       </c>
       <c r="R26" t="n">
-        <v>7246903</v>
+        <v>7246959</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3649,6 +3553,11 @@
           <t>2024-08-04</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På 2 sälgar</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3660,22 +3569,17 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL26" t="inlineStr">
-        <is>
-          <t>Lutande död gran</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Picea abies # Lutande död gran</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3693,15 +3597,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119506881</v>
+        <v>119506844</v>
       </c>
       <c r="B27" t="n">
-        <v>90576</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3709,21 +3608,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3733,10 +3632,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>541753</v>
+        <v>541477</v>
       </c>
       <c r="R27" t="n">
-        <v>7247186</v>
+        <v>7246915</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3782,22 +3681,17 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL27" t="inlineStr">
-        <is>
-          <t>Granlåga, avbarkad</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga, avbarkad</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3815,37 +3709,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119506821</v>
+        <v>119506845</v>
       </c>
       <c r="B28" t="n">
-        <v>91005</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3855,10 +3744,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>541524</v>
+        <v>541496</v>
       </c>
       <c r="R28" t="n">
-        <v>7247178</v>
+        <v>7247059</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3904,22 +3793,17 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL28" t="inlineStr">
-        <is>
-          <t>Granlåga grov</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga grov</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3937,37 +3821,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119506825</v>
+        <v>119506846</v>
       </c>
       <c r="B29" t="n">
-        <v>91005</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3977,10 +3856,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>541556</v>
+        <v>541493</v>
       </c>
       <c r="R29" t="n">
-        <v>7247196</v>
+        <v>7247094</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4026,22 +3905,17 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL29" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4059,15 +3933,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119506843</v>
+        <v>119506848</v>
       </c>
       <c r="B30" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4099,10 +3968,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>541611</v>
+        <v>541498</v>
       </c>
       <c r="R30" t="n">
-        <v>7246959</v>
+        <v>7247159</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4135,11 +4004,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-08-04</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På 2 sälgar</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4181,15 +4045,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119506800</v>
+        <v>119506849</v>
       </c>
       <c r="B31" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4197,42 +4056,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>541377</v>
+        <v>541555</v>
       </c>
       <c r="R31" t="n">
-        <v>7246829</v>
+        <v>7247205</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4267,11 +4118,6 @@
           <t>2024-08-04</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>3 stycken bohål i granhögstubbe</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4283,22 +4129,17 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL31" t="inlineStr">
-        <is>
-          <t>Granhögstubbe</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4316,15 +4157,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119506753</v>
+        <v>119506850</v>
       </c>
       <c r="B32" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4332,39 +4168,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>541495</v>
+        <v>541544</v>
       </c>
       <c r="R32" t="n">
-        <v>7247049</v>
+        <v>7247215</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4399,11 +4230,6 @@
           <t>2024-08-04</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4415,17 +4241,17 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4443,15 +4269,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119506794</v>
+        <v>119506851</v>
       </c>
       <c r="B33" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4459,39 +4280,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>541533</v>
+        <v>541616</v>
       </c>
       <c r="R33" t="n">
-        <v>7247171</v>
+        <v>7246971</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4526,11 +4342,6 @@
           <t>2024-08-04</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Barksprätt, färska</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4542,17 +4353,17 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4570,15 +4381,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119506879</v>
+        <v>119506852</v>
       </c>
       <c r="B34" t="n">
-        <v>90576</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4586,21 +4392,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4610,10 +4416,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>541392</v>
+        <v>541629</v>
       </c>
       <c r="R34" t="n">
-        <v>7246823</v>
+        <v>7246933</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4652,24 +4458,24 @@
         <v>0</v>
       </c>
       <c r="AE34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4687,15 +4493,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119506886</v>
+        <v>119506853</v>
       </c>
       <c r="B35" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4703,21 +4504,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4727,10 +4528,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>541671</v>
+        <v>541641</v>
       </c>
       <c r="R35" t="n">
-        <v>7247092</v>
+        <v>7246887</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4776,22 +4577,17 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL35" t="inlineStr">
-        <is>
-          <t>levande</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Picea abies # levande</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4809,15 +4605,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119506778</v>
+        <v>119506854</v>
       </c>
       <c r="B36" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4825,39 +4616,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>541526</v>
+        <v>541634</v>
       </c>
       <c r="R36" t="n">
-        <v>7247213</v>
+        <v>7246902</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4892,11 +4678,6 @@
           <t>2024-08-04</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Barksprätt, färska</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4908,17 +4689,17 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4936,15 +4717,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119506783</v>
+        <v>119506855</v>
       </c>
       <c r="B37" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4952,39 +4728,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>541672</v>
+        <v>541536</v>
       </c>
       <c r="R37" t="n">
-        <v>7247167</v>
+        <v>7246870</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5019,11 +4790,6 @@
           <t>2024-08-04</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5035,17 +4801,22 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AL37" t="inlineStr">
+        <is>
+          <t>Död rönn</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia # Död rönn</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5063,15 +4834,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119506733</v>
+        <v>119506856</v>
       </c>
       <c r="B38" t="n">
-        <v>90562</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5079,21 +4845,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5103,10 +4869,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>541453</v>
+        <v>541590</v>
       </c>
       <c r="R38" t="n">
-        <v>7246859</v>
+        <v>7246904</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5141,6 +4907,11 @@
           <t>2024-08-04</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På 2 rönnar</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5152,22 +4923,17 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL38" t="inlineStr">
-        <is>
-          <t>Granhögstubbe</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5185,37 +4951,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119506739</v>
+        <v>119506857</v>
       </c>
       <c r="B39" t="n">
-        <v>91254</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3298</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5225,10 +4986,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>541700</v>
+        <v>541453</v>
       </c>
       <c r="R39" t="n">
-        <v>7247194</v>
+        <v>7246885</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5263,11 +5024,6 @@
           <t>2024-08-04</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Vid basen</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -5279,17 +5035,17 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5307,15 +5063,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119506848</v>
+        <v>119506858</v>
       </c>
       <c r="B40" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5347,10 +5098,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>541498</v>
+        <v>541499</v>
       </c>
       <c r="R40" t="n">
-        <v>7247159</v>
+        <v>7246880</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5396,17 +5147,17 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5424,15 +5175,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119506856</v>
+        <v>119506753</v>
       </c>
       <c r="B41" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5440,34 +5186,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>541590</v>
+        <v>541495</v>
       </c>
       <c r="R41" t="n">
-        <v>7246904</v>
+        <v>7247049</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5504,7 +5255,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På 2 rönnar</t>
+          <t>Ringhack, äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5518,17 +5269,17 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5546,15 +5297,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119506842</v>
+        <v>119506754</v>
       </c>
       <c r="B42" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5562,34 +5308,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>541629</v>
+        <v>541563</v>
       </c>
       <c r="R42" t="n">
-        <v>7246917</v>
+        <v>7247188</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5626,7 +5377,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack, äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5640,17 +5391,17 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5668,50 +5419,50 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119506932</v>
+        <v>119506771</v>
       </c>
       <c r="B43" t="n">
-        <v>90957</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4217</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>541480</v>
+        <v>541407</v>
       </c>
       <c r="R43" t="n">
-        <v>7247090</v>
+        <v>7246819</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5744,6 +5495,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack, färska</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5785,50 +5541,50 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119506735</v>
+        <v>119506778</v>
       </c>
       <c r="B44" t="n">
-        <v>91254</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>541604</v>
+        <v>541526</v>
       </c>
       <c r="R44" t="n">
-        <v>7246915</v>
+        <v>7247213</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5865,7 +5621,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Barksprätt, färska</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5887,14 +5643,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL44" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5912,15 +5663,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119506845</v>
+        <v>119506779</v>
       </c>
       <c r="B45" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5928,34 +5674,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>541496</v>
+        <v>541700</v>
       </c>
       <c r="R45" t="n">
-        <v>7247059</v>
+        <v>7247194</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5990,6 +5741,11 @@
           <t>2024-08-04</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Barksprätt, färska</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -6001,17 +5757,17 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6029,15 +5785,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119506793</v>
+        <v>119506782</v>
       </c>
       <c r="B46" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6065,7 +5816,7 @@
       <c r="I46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -6074,10 +5825,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>541460</v>
+        <v>541469</v>
       </c>
       <c r="R46" t="n">
-        <v>7246892</v>
+        <v>7246839</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6114,7 +5865,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Barksprätt, färska</t>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6156,15 +5907,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119506862</v>
+        <v>119506783</v>
       </c>
       <c r="B47" t="n">
-        <v>90954</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6172,36 +5918,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6040186</v>
+        <v>100109</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>541476</v>
+        <v>541672</v>
       </c>
       <c r="R47" t="n">
-        <v>7247094</v>
+        <v>7247167</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6238,7 +5987,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Minst 22 fruktkroppar</t>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6247,7 +5996,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6261,14 +6009,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL47" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6286,15 +6029,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119506860</v>
+        <v>119506784</v>
       </c>
       <c r="B48" t="n">
-        <v>90954</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6302,32 +6040,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6040186</v>
+        <v>100109</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>541527</v>
+        <v>541374</v>
       </c>
       <c r="R48" t="n">
-        <v>7247215</v>
+        <v>7246832</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6362,13 +6107,17 @@
           <t>2024-08-04</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6382,14 +6131,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL48" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6407,15 +6151,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119506861</v>
+        <v>119506793</v>
       </c>
       <c r="B49" t="n">
-        <v>90954</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6423,32 +6162,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6040186</v>
+        <v>100109</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>541546</v>
+        <v>541460</v>
       </c>
       <c r="R49" t="n">
-        <v>7247187</v>
+        <v>7246892</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6483,13 +6229,17 @@
           <t>2024-08-04</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Barksprätt, färska</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6503,14 +6253,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL49" t="inlineStr">
-        <is>
-          <t>Granhögstubbe</t>
-        </is>
-      </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6528,50 +6273,50 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119506826</v>
+        <v>119506794</v>
       </c>
       <c r="B50" t="n">
-        <v>91005</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>541453</v>
+        <v>541533</v>
       </c>
       <c r="R50" t="n">
-        <v>7246866</v>
+        <v>7247171</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6606,6 +6351,11 @@
           <t>2024-08-04</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Barksprätt, färska</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -6625,14 +6375,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL50" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6650,50 +6395,53 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119506824</v>
+        <v>119506800</v>
       </c>
       <c r="B51" t="n">
-        <v>91005</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>541480</v>
+        <v>541377</v>
       </c>
       <c r="R51" t="n">
-        <v>7247086</v>
+        <v>7246829</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6728,6 +6476,11 @@
           <t>2024-08-04</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>3 stycken bohål i granhögstubbe</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6749,12 +6502,12 @@
       </c>
       <c r="AL51" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Granhögstubbe</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Picea abies # Granhögstubbe</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6772,50 +6525,54 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119506844</v>
+        <v>119506801</v>
       </c>
       <c r="B52" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>541477</v>
+        <v>541465</v>
       </c>
       <c r="R52" t="n">
-        <v>7246915</v>
+        <v>7247101</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6842,12 +6599,17 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Stöttes</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6858,21 +6620,6 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6889,15 +6636,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119506909</v>
+        <v>119506804</v>
       </c>
       <c r="B53" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6905,34 +6647,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>541625</v>
+        <v>541479</v>
       </c>
       <c r="R53" t="n">
-        <v>7247035</v>
+        <v>7247082</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6975,26 +6722,6 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL53" t="inlineStr">
-        <is>
-          <t>Granhögstubbe</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Picea abies # Granhögstubbe</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -7011,15 +6738,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119506902</v>
+        <v>119506936</v>
       </c>
       <c r="B54" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87099</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7027,34 +6749,41 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5432</v>
+        <v>249278</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(Pers.) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>541589</v>
+        <v>541297</v>
       </c>
       <c r="R54" t="n">
-        <v>7246895</v>
+        <v>7246784</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7095,28 +6824,9 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL54" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -7133,15 +6843,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119506833</v>
+        <v>119506860</v>
       </c>
       <c r="B55" t="n">
-        <v>90846</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92329</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7149,38 +6854,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>658</v>
+        <v>6040186</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>541476</v>
+        <v>541527</v>
       </c>
       <c r="R55" t="n">
-        <v>7247092</v>
+        <v>7247215</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7221,6 +6925,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -7259,59 +6964,48 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119506801</v>
+        <v>119506861</v>
       </c>
       <c r="B56" t="n">
-        <v>56522</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92329</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100138</v>
+        <v>6040186</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>541465</v>
+        <v>541546</v>
       </c>
       <c r="R56" t="n">
-        <v>7247101</v>
+        <v>7247187</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7338,17 +7032,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-08-04</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Stöttes</t>
+          <t>2024-08-04</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7357,8 +7046,29 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL56" t="inlineStr">
+        <is>
+          <t>Granhögstubbe</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Picea abies # Granhögstubbe</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -7375,15 +7085,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119506857</v>
+        <v>119506862</v>
       </c>
       <c r="B57" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92329</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7391,34 +7096,41 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>6040186</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>541453</v>
+        <v>541476</v>
       </c>
       <c r="R57" t="n">
-        <v>7246885</v>
+        <v>7247094</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7453,28 +7165,39 @@
           <t>2024-08-04</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Minst 22 fruktkroppar</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL57" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7492,55 +7215,43 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119506771</v>
+        <v>119506722</v>
       </c>
       <c r="B58" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92285</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6331024</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis delicata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Miettinen &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>541407</v>
+        <v>541455</v>
       </c>
       <c r="R58" t="n">
-        <v>7246819</v>
+        <v>7246861</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7577,7 +7288,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhack, färska</t>
+          <t>Kollekt På ved under ullticka Artbestämnd via mikroskopering</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7586,6 +7297,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7616,376 +7328,6 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>119506782</v>
-      </c>
-      <c r="B59" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E59" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>Matsdal, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q59" t="n">
-        <v>541469</v>
-      </c>
-      <c r="R59" t="n">
-        <v>7246839</v>
-      </c>
-      <c r="S59" t="n">
-        <v>10</v>
-      </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y59" t="inlineStr">
-        <is>
-          <t>2024-08-04</t>
-        </is>
-      </c>
-      <c r="AA59" t="inlineStr">
-        <is>
-          <t>2024-08-04</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
-        </is>
-      </c>
-      <c r="AD59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AT59" t="inlineStr"/>
-      <c r="AW59" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AY59" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>119506900</v>
-      </c>
-      <c r="B60" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E60" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>Matsdal, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q60" t="n">
-        <v>541530</v>
-      </c>
-      <c r="R60" t="n">
-        <v>7247230</v>
-      </c>
-      <c r="S60" t="n">
-        <v>10</v>
-      </c>
-      <c r="T60" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U60" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W60" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y60" t="inlineStr">
-        <is>
-          <t>2024-08-04</t>
-        </is>
-      </c>
-      <c r="AA60" t="inlineStr">
-        <is>
-          <t>2024-08-04</t>
-        </is>
-      </c>
-      <c r="AD60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL60" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga</t>
-        </is>
-      </c>
-      <c r="AT60" t="inlineStr"/>
-      <c r="AW60" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AY60" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>119506877</v>
-      </c>
-      <c r="B61" t="n">
-        <v>91912</v>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E61" t="n">
-        <v>1179</v>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Gräddticka</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>Perenniporia subacida</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>(Peck) Donk</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>Matsdal, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q61" t="n">
-        <v>541388</v>
-      </c>
-      <c r="R61" t="n">
-        <v>7246830</v>
-      </c>
-      <c r="S61" t="n">
-        <v>10</v>
-      </c>
-      <c r="T61" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U61" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V61" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W61" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y61" t="inlineStr">
-        <is>
-          <t>2024-08-04</t>
-        </is>
-      </c>
-      <c r="AA61" t="inlineStr">
-        <is>
-          <t>2024-08-04</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Kollekt Artbestämnd via mikroskopering</t>
-        </is>
-      </c>
-      <c r="AD61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF61" t="inlineStr"/>
-      <c r="AG61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AT61" t="inlineStr"/>
-      <c r="AW61" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AY61" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
